--- a/output_boron/boron_Intermediate_martinez-boti_2015.xlsx
+++ b/output_boron/boron_Intermediate_martinez-boti_2015.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1038/nature14145</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_martinez-boti_2015.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_martinez-boti_2015_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1379,6 +1379,9 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
+    <t xml:space="preserve">added age uncertainty based on LR04, used revised age model of de la Vega et al. 2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">Globigerinoides ruber white</t>
   </si>
   <si>
@@ -1400,6 +1403,9 @@
     <t xml:space="preserve">ODP 999_A_9_3_22_24</t>
   </si>
   <si>
+    <t xml:space="preserve">added age uncertainty based on LR04, recalculated age following updated age model of de la Vega et al. 2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 999_A_9_3_51_53</t>
   </si>
   <si>
@@ -1611,6 +1617,9 @@
   </si>
   <si>
     <t xml:space="preserve">ODP 662_____</t>
+  </si>
+  <si>
+    <t xml:space="preserve">added age uncertainty based on LR04</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1627,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1678,12 +1687,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1797,7 +1800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1879,7 +1882,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2486,7 +2488,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2502,10 +2504,10 @@
         <v>-78.73</v>
       </c>
       <c r="H5" t="n">
-        <v>2.33782251</v>
-      </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+        <v>2.34014</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.006</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2513,20 +2515,20 @@
       <c r="K5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L5" t="e">
-        <v>#N/A</v>
+      <c r="L5" t="s">
+        <v>245</v>
       </c>
       <c r="M5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q5" t="n">
         <v>20.23352</v>
@@ -2558,12 +2560,12 @@
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2579,10 +2581,10 @@
         <v>-78.73</v>
       </c>
       <c r="H6" t="n">
-        <v>2.346710693</v>
-      </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+        <v>2.35085</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.006</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2590,20 +2592,20 @@
       <c r="K6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L6" t="e">
-        <v>#N/A</v>
+      <c r="L6" t="s">
+        <v>245</v>
       </c>
       <c r="M6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q6" t="n">
         <v>20.20777</v>
@@ -2635,12 +2637,12 @@
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2656,10 +2658,10 @@
         <v>-78.73</v>
       </c>
       <c r="H7" t="n">
-        <v>2.352717773</v>
-      </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+        <v>2.35808</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.006</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2667,20 +2669,20 @@
       <c r="K7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L7" t="e">
-        <v>#N/A</v>
+      <c r="L7" t="s">
+        <v>245</v>
       </c>
       <c r="M7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7" t="n">
         <v>20.40347</v>
@@ -2712,12 +2714,12 @@
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2733,10 +2735,10 @@
         <v>-78.73</v>
       </c>
       <c r="H8" t="n">
-        <v>2.362218994</v>
-      </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+        <v>2.36861</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.006</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2744,20 +2746,20 @@
       <c r="K8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L8" t="e">
-        <v>#N/A</v>
+      <c r="L8" t="s">
+        <v>253</v>
       </c>
       <c r="M8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q8" t="n">
         <v>19.422</v>
@@ -2789,12 +2791,12 @@
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2810,10 +2812,10 @@
         <v>-78.73</v>
       </c>
       <c r="H9" t="n">
-        <v>2.372198242</v>
-      </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+        <v>2.37892</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.006</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2821,20 +2823,20 @@
       <c r="K9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L9" t="e">
-        <v>#N/A</v>
+      <c r="L9" t="s">
+        <v>245</v>
       </c>
       <c r="M9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q9" t="n">
         <v>19.65151</v>
@@ -2866,12 +2868,12 @@
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2887,10 +2889,10 @@
         <v>-78.73</v>
       </c>
       <c r="H10" t="n">
-        <v>2.381290283</v>
-      </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+        <v>2.38839</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.006</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -2898,20 +2900,20 @@
       <c r="K10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L10" t="e">
-        <v>#N/A</v>
+      <c r="L10" t="s">
+        <v>245</v>
       </c>
       <c r="M10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q10" t="n">
         <v>19.89014</v>
@@ -2943,12 +2945,12 @@
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2964,10 +2966,10 @@
         <v>-78.73</v>
       </c>
       <c r="H11" t="n">
-        <v>2.389315918</v>
-      </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+        <v>2.39671</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.006</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -2975,20 +2977,20 @@
       <c r="K11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L11" t="e">
-        <v>#N/A</v>
+      <c r="L11" t="s">
+        <v>245</v>
       </c>
       <c r="M11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q11" t="n">
         <v>19.83353</v>
@@ -3020,12 +3022,12 @@
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3041,10 +3043,10 @@
         <v>-78.73</v>
       </c>
       <c r="H12" t="n">
-        <v>2.410920166</v>
-      </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+        <v>2.41093</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.006</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3052,20 +3054,20 @@
       <c r="K12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L12" t="e">
-        <v>#N/A</v>
+      <c r="L12" t="s">
+        <v>245</v>
       </c>
       <c r="M12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q12" t="n">
         <v>20.56797</v>
@@ -3097,12 +3099,12 @@
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3118,10 +3120,10 @@
         <v>-78.73</v>
       </c>
       <c r="H13" t="n">
-        <v>2.424888916</v>
-      </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+        <v>2.42663</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.006</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3129,20 +3131,20 @@
       <c r="K13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L13" t="e">
-        <v>#N/A</v>
+      <c r="L13" t="s">
+        <v>245</v>
       </c>
       <c r="M13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q13" t="n">
         <v>20.10464</v>
@@ -3174,12 +3176,12 @@
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3195,10 +3197,10 @@
         <v>-78.73</v>
       </c>
       <c r="H14" t="n">
-        <v>2.451231689</v>
-      </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+        <v>2.45451</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.006</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3206,20 +3208,20 @@
       <c r="K14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L14" t="e">
-        <v>#N/A</v>
+      <c r="L14" t="s">
+        <v>245</v>
       </c>
       <c r="M14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q14" t="n">
         <v>20.1955</v>
@@ -3251,12 +3253,12 @@
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3272,10 +3274,10 @@
         <v>-78.73</v>
       </c>
       <c r="H15" t="n">
-        <v>2.474494141</v>
-      </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+        <v>2.47382</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.006</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3283,20 +3285,20 @@
       <c r="K15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L15" t="e">
-        <v>#N/A</v>
+      <c r="L15" t="s">
+        <v>245</v>
       </c>
       <c r="M15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q15" t="n">
         <v>20.03869</v>
@@ -3328,12 +3330,12 @@
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3349,10 +3351,10 @@
         <v>-78.73</v>
       </c>
       <c r="H16" t="n">
-        <v>2.50040332</v>
-      </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+        <v>2.49734</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.006</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3360,20 +3362,20 @@
       <c r="K16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L16" t="e">
-        <v>#N/A</v>
+      <c r="L16" t="s">
+        <v>245</v>
       </c>
       <c r="M16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q16" t="n">
         <v>19.90691</v>
@@ -3405,12 +3407,12 @@
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3426,10 +3428,10 @@
         <v>-78.73</v>
       </c>
       <c r="H17" t="n">
-        <v>2.501402588</v>
-      </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+        <v>2.4983</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.006</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3437,20 +3439,20 @@
       <c r="K17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L17" t="e">
-        <v>#N/A</v>
+      <c r="L17" t="s">
+        <v>245</v>
       </c>
       <c r="M17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q17" t="n">
         <v>19.87513</v>
@@ -3482,12 +3484,12 @@
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3503,10 +3505,10 @@
         <v>-78.73</v>
       </c>
       <c r="H18" t="n">
-        <v>2.521932373</v>
-      </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+        <v>2.51716</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.006</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3514,20 +3516,20 @@
       <c r="K18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L18" t="e">
-        <v>#N/A</v>
+      <c r="L18" t="s">
+        <v>245</v>
       </c>
       <c r="M18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q18" t="n">
         <v>20.70584</v>
@@ -3559,12 +3561,12 @@
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3580,10 +3582,10 @@
         <v>-78.73</v>
       </c>
       <c r="H19" t="n">
-        <v>2.545154541</v>
-      </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+        <v>2.54044</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.006</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3591,20 +3593,20 @@
       <c r="K19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L19" t="e">
-        <v>#N/A</v>
+      <c r="L19" t="s">
+        <v>245</v>
       </c>
       <c r="M19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19" t="n">
         <v>19.99687</v>
@@ -3636,12 +3638,12 @@
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3657,10 +3659,10 @@
         <v>-78.73</v>
       </c>
       <c r="H20" t="n">
-        <v>2.561898438</v>
-      </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+        <v>2.5724</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.006</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3668,20 +3670,20 @@
       <c r="K20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L20" t="e">
-        <v>#N/A</v>
+      <c r="L20" t="s">
+        <v>245</v>
       </c>
       <c r="M20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q20" t="n">
         <v>20.31609</v>
@@ -3713,12 +3715,12 @@
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3734,10 +3736,10 @@
         <v>-78.73</v>
       </c>
       <c r="H21" t="n">
-        <v>2.579425049</v>
-      </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+        <v>2.5865</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.006</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3745,20 +3747,20 @@
       <c r="K21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L21" t="e">
-        <v>#N/A</v>
+      <c r="L21" t="s">
+        <v>245</v>
       </c>
       <c r="M21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q21" t="n">
         <v>20.03998</v>
@@ -3790,12 +3792,12 @@
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3811,10 +3813,10 @@
         <v>-78.73</v>
       </c>
       <c r="H22" t="n">
-        <v>2.594836426</v>
-      </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+        <v>2.60034</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.006</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3822,20 +3824,20 @@
       <c r="K22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L22" t="e">
-        <v>#N/A</v>
+      <c r="L22" t="s">
+        <v>245</v>
       </c>
       <c r="M22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22" t="n">
         <v>19.93046</v>
@@ -3867,12 +3869,12 @@
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3888,10 +3890,10 @@
         <v>-78.73</v>
       </c>
       <c r="H23" t="n">
-        <v>2.615069336</v>
-      </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+        <v>2.61869</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.006</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -3899,20 +3901,20 @@
       <c r="K23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L23" t="e">
-        <v>#N/A</v>
+      <c r="L23" t="s">
+        <v>245</v>
       </c>
       <c r="M23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q23" t="n">
         <v>20.4209</v>
@@ -3944,12 +3946,12 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3965,10 +3967,10 @@
         <v>-78.73</v>
       </c>
       <c r="H24" t="n">
-        <v>2.624496094</v>
-      </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+        <v>2.62686</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.006</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -3976,20 +3978,20 @@
       <c r="K24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L24" t="e">
-        <v>#N/A</v>
+      <c r="L24" t="s">
+        <v>245</v>
       </c>
       <c r="M24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24" t="n">
         <v>20.23123</v>
@@ -4021,12 +4023,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4042,10 +4044,10 @@
         <v>-78.73</v>
       </c>
       <c r="H25" t="n">
-        <v>2.630914795</v>
-      </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+        <v>2.63274</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.006</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4053,20 +4055,20 @@
       <c r="K25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L25" t="e">
-        <v>#N/A</v>
+      <c r="L25" t="s">
+        <v>245</v>
       </c>
       <c r="M25" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q25" t="n">
         <v>20.79829</v>
@@ -4098,12 +4100,12 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4119,10 +4121,10 @@
         <v>-78.73</v>
       </c>
       <c r="H26" t="n">
-        <v>2.648257813</v>
-      </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+        <v>2.64736</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.006</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4130,20 +4132,20 @@
       <c r="K26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L26" t="e">
-        <v>#N/A</v>
+      <c r="L26" t="s">
+        <v>245</v>
       </c>
       <c r="M26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q26" t="n">
         <v>20.42573</v>
@@ -4175,12 +4177,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4196,10 +4198,10 @@
         <v>-78.73</v>
       </c>
       <c r="H27" t="n">
-        <v>2.664697021</v>
-      </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+        <v>2.66138</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.006</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4207,20 +4209,20 @@
       <c r="K27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L27" t="e">
-        <v>#N/A</v>
+      <c r="L27" t="s">
+        <v>245</v>
       </c>
       <c r="M27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q27" t="n">
         <v>20.3588</v>
@@ -4252,12 +4254,12 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4273,10 +4275,10 @@
         <v>-78.73</v>
       </c>
       <c r="H28" t="n">
-        <v>2.673016113</v>
-      </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+        <v>2.67105</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.006</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4284,20 +4286,20 @@
       <c r="K28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L28" t="e">
-        <v>#N/A</v>
+      <c r="L28" t="s">
+        <v>245</v>
       </c>
       <c r="M28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q28" t="n">
         <v>20.57567</v>
@@ -4329,12 +4331,12 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4350,10 +4352,10 @@
         <v>-78.73</v>
       </c>
       <c r="H29" t="n">
-        <v>2.680359375</v>
-      </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+        <v>2.67921</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.006</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -4361,20 +4363,20 @@
       <c r="K29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L29" t="e">
-        <v>#N/A</v>
+      <c r="L29" t="s">
+        <v>245</v>
       </c>
       <c r="M29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q29" t="n">
         <v>20.04105</v>
@@ -4406,12 +4408,12 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4427,10 +4429,10 @@
         <v>-78.73</v>
       </c>
       <c r="H30" t="n">
-        <v>2.686560303</v>
-      </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+        <v>2.68616</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.006</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -4438,20 +4440,20 @@
       <c r="K30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L30" t="e">
-        <v>#N/A</v>
+      <c r="L30" t="s">
+        <v>245</v>
       </c>
       <c r="M30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="n">
         <v>20.31268</v>
@@ -4483,12 +4485,12 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4504,10 +4506,10 @@
         <v>-78.73</v>
       </c>
       <c r="H31" t="n">
-        <v>2.695158203</v>
-      </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+        <v>2.69825</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.006</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -4515,20 +4517,20 @@
       <c r="K31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L31" t="e">
-        <v>#N/A</v>
+      <c r="L31" t="s">
+        <v>245</v>
       </c>
       <c r="M31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O31" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q31" t="n">
         <v>20.34747</v>
@@ -4560,12 +4562,12 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4581,10 +4583,10 @@
         <v>-78.73</v>
       </c>
       <c r="H32" t="n">
-        <v>2.700043457</v>
-      </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+        <v>2.70551</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.006</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -4592,20 +4594,20 @@
       <c r="K32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L32" t="e">
-        <v>#N/A</v>
+      <c r="L32" t="s">
+        <v>245</v>
       </c>
       <c r="M32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q32" t="n">
         <v>20.74582</v>
@@ -4637,12 +4639,12 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4658,10 +4660,10 @@
         <v>-78.73</v>
       </c>
       <c r="H33" t="n">
-        <v>2.703202637</v>
-      </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+        <v>2.71004</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.006</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -4669,20 +4671,20 @@
       <c r="K33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L33" t="e">
-        <v>#N/A</v>
+      <c r="L33" t="s">
+        <v>245</v>
       </c>
       <c r="M33" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q33" t="n">
         <v>20.05298</v>
@@ -4714,12 +4716,12 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4735,10 +4737,10 @@
         <v>-78.73</v>
       </c>
       <c r="H34" t="n">
-        <v>2.707214111</v>
-      </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+        <v>2.71609</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.006</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -4746,20 +4748,20 @@
       <c r="K34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L34" t="e">
-        <v>#N/A</v>
+      <c r="L34" t="s">
+        <v>245</v>
       </c>
       <c r="M34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q34" t="n">
         <v>20.5103</v>
@@ -4791,12 +4793,12 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4812,10 +4814,10 @@
         <v>-78.73</v>
       </c>
       <c r="H35" t="n">
-        <v>2.745515625</v>
-      </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+        <v>2.74451</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.006</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -4823,20 +4825,20 @@
       <c r="K35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L35" t="e">
-        <v>#N/A</v>
+      <c r="L35" t="s">
+        <v>245</v>
       </c>
       <c r="M35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q35" t="n">
         <v>19.99044</v>
@@ -4868,12 +4870,12 @@
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4889,10 +4891,10 @@
         <v>-78.73</v>
       </c>
       <c r="H36" t="n">
-        <v>2.751482666</v>
-      </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+        <v>2.75111</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.006</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -4900,20 +4902,20 @@
       <c r="K36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L36" t="e">
-        <v>#N/A</v>
+      <c r="L36" t="s">
+        <v>245</v>
       </c>
       <c r="M36" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O36" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q36" t="n">
         <v>20.11</v>
@@ -4945,12 +4947,12 @@
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -4966,10 +4968,10 @@
         <v>-78.73</v>
       </c>
       <c r="H37" t="n">
-        <v>2.764187012</v>
-      </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+        <v>2.76459</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.006</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -4977,20 +4979,20 @@
       <c r="K37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L37" t="e">
-        <v>#N/A</v>
+      <c r="L37" t="s">
+        <v>245</v>
       </c>
       <c r="M37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q37" t="n">
         <v>19.85953</v>
@@ -5022,12 +5024,12 @@
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5043,10 +5045,10 @@
         <v>-78.73</v>
       </c>
       <c r="H38" t="n">
-        <v>2.777480957</v>
-      </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+        <v>2.77807</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.006</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -5054,20 +5056,20 @@
       <c r="K38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L38" t="e">
-        <v>#N/A</v>
+      <c r="L38" t="s">
+        <v>245</v>
       </c>
       <c r="M38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q38" t="n">
         <v>20.37055</v>
@@ -5099,12 +5101,12 @@
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5120,10 +5122,10 @@
         <v>-78.73</v>
       </c>
       <c r="H39" t="n">
-        <v>2.798543701</v>
-      </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+        <v>2.79952</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.006</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -5131,20 +5133,20 @@
       <c r="K39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L39" t="e">
-        <v>#N/A</v>
+      <c r="L39" t="s">
+        <v>245</v>
       </c>
       <c r="M39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q39" t="n">
         <v>20.39716</v>
@@ -5176,12 +5178,12 @@
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5197,10 +5199,10 @@
         <v>-78.73</v>
       </c>
       <c r="H40" t="n">
-        <v>2.83017627</v>
-      </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+        <v>2.82186</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.006</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -5208,20 +5210,20 @@
       <c r="K40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L40" t="e">
-        <v>#N/A</v>
+      <c r="L40" t="s">
+        <v>245</v>
       </c>
       <c r="M40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q40" t="n">
         <v>20.1979</v>
@@ -5253,12 +5255,12 @@
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5274,10 +5276,10 @@
         <v>-78.73</v>
       </c>
       <c r="H41" t="n">
-        <v>2.831683838</v>
-      </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+        <v>2.82345</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.006</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -5285,20 +5287,20 @@
       <c r="K41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L41" t="e">
-        <v>#N/A</v>
+      <c r="L41" t="s">
+        <v>245</v>
       </c>
       <c r="M41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q41" t="n">
         <v>19.87284</v>
@@ -5330,12 +5332,12 @@
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5351,10 +5353,10 @@
         <v>-78.73</v>
       </c>
       <c r="H42" t="n">
-        <v>2.838900635</v>
-      </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+        <v>2.83234</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.006</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -5362,20 +5364,20 @@
       <c r="K42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L42" t="e">
-        <v>#N/A</v>
+      <c r="L42" t="s">
+        <v>245</v>
       </c>
       <c r="M42" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q42" t="n">
         <v>19.67065</v>
@@ -5407,12 +5409,12 @@
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5428,10 +5430,10 @@
         <v>-78.73</v>
       </c>
       <c r="H43" t="n">
-        <v>2.849182373</v>
-      </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+        <v>2.84505</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.006</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -5439,20 +5441,20 @@
       <c r="K43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L43" t="e">
-        <v>#N/A</v>
+      <c r="L43" t="s">
+        <v>245</v>
       </c>
       <c r="M43" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N43" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P43" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q43" t="n">
         <v>20.16006</v>
@@ -5484,12 +5486,12 @@
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5505,10 +5507,10 @@
         <v>-78.73</v>
       </c>
       <c r="H44" t="n">
-        <v>2.858321045</v>
-      </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+        <v>2.88285</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.006</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -5516,20 +5518,20 @@
       <c r="K44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L44" t="e">
-        <v>#N/A</v>
+      <c r="L44" t="s">
+        <v>245</v>
       </c>
       <c r="M44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N44" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q44" t="n">
         <v>19.31226</v>
@@ -5561,12 +5563,12 @@
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5582,10 +5584,10 @@
         <v>-78.73</v>
       </c>
       <c r="H45" t="n">
-        <v>2.912384277</v>
-      </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+        <v>2.9162</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.006</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -5593,20 +5595,20 @@
       <c r="K45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L45" t="e">
-        <v>#N/A</v>
+      <c r="L45" t="s">
+        <v>245</v>
       </c>
       <c r="M45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45" t="n">
         <v>19.70327</v>
@@ -5638,12 +5640,12 @@
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5659,10 +5661,10 @@
         <v>-78.73</v>
       </c>
       <c r="H46" t="n">
-        <v>2.92355957</v>
-      </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+        <v>2.927</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.006</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -5670,20 +5672,20 @@
       <c r="K46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L46" t="e">
-        <v>#N/A</v>
+      <c r="L46" t="s">
+        <v>245</v>
       </c>
       <c r="M46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q46" t="n">
         <v>19.65744</v>
@@ -5715,12 +5717,12 @@
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5736,10 +5738,10 @@
         <v>-78.73</v>
       </c>
       <c r="H47" t="n">
-        <v>2.941578125</v>
-      </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+        <v>2.94297</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.006</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -5747,20 +5749,20 @@
       <c r="K47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L47" t="e">
-        <v>#N/A</v>
+      <c r="L47" t="s">
+        <v>245</v>
       </c>
       <c r="M47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O47" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q47" t="n">
         <v>19.9735</v>
@@ -5792,12 +5794,12 @@
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5813,10 +5815,10 @@
         <v>-78.73</v>
       </c>
       <c r="H48" t="n">
-        <v>2.950492676</v>
-      </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+        <v>2.95022</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.006</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -5824,20 +5826,20 @@
       <c r="K48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L48" t="e">
-        <v>#N/A</v>
+      <c r="L48" t="s">
+        <v>245</v>
       </c>
       <c r="M48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N48" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P48" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q48" t="n">
         <v>19.75671</v>
@@ -5869,12 +5871,12 @@
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -5890,10 +5892,10 @@
         <v>-78.73</v>
       </c>
       <c r="H49" t="n">
-        <v>2.951161377</v>
-      </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+        <v>2.95022</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.006</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -5901,20 +5903,20 @@
       <c r="K49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L49" t="e">
-        <v>#N/A</v>
+      <c r="L49" t="s">
+        <v>245</v>
       </c>
       <c r="M49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q49" t="n">
         <v>19.46</v>
@@ -5946,12 +5948,12 @@
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B50" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" t="s">
         <v>242</v>
       </c>
       <c r="D50" t="s">
@@ -5967,10 +5969,10 @@
         <v>-78.73</v>
       </c>
       <c r="H50" t="n">
-        <v>2.959599365</v>
-      </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+        <v>2.95669</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.006</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -5978,20 +5980,20 @@
       <c r="K50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L50" t="e">
-        <v>#N/A</v>
+      <c r="L50" t="s">
+        <v>245</v>
       </c>
       <c r="M50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q50" t="n">
         <v>20.00959</v>
@@ -6023,12 +6025,12 @@
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" t="s">
         <v>242</v>
       </c>
       <c r="D51" t="s">
@@ -6044,10 +6046,10 @@
         <v>-78.73</v>
       </c>
       <c r="H51" t="n">
-        <v>2.978066406</v>
-      </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+        <v>2.9717</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.006</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -6055,20 +6057,20 @@
       <c r="K51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L51" t="e">
-        <v>#N/A</v>
+      <c r="L51" t="s">
+        <v>245</v>
       </c>
       <c r="M51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q51" t="n">
         <v>20.02403</v>
@@ -6100,12 +6102,12 @@
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B52" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" t="s">
         <v>242</v>
       </c>
       <c r="D52" t="s">
@@ -6121,10 +6123,10 @@
         <v>-78.73</v>
       </c>
       <c r="H52" t="n">
-        <v>3.002813721</v>
-      </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+        <v>2.99811</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.015</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -6132,20 +6134,20 @@
       <c r="K52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L52" t="e">
-        <v>#N/A</v>
+      <c r="L52" t="s">
+        <v>245</v>
       </c>
       <c r="M52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q52" t="n">
         <v>19.7427</v>
@@ -6177,12 +6179,12 @@
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" t="s">
         <v>242</v>
       </c>
       <c r="D53" t="s">
@@ -6198,10 +6200,10 @@
         <v>-78.73</v>
       </c>
       <c r="H53" t="n">
-        <v>3.010996094</v>
-      </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+        <v>3.00665</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.015</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -6209,20 +6211,20 @@
       <c r="K53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L53" t="e">
-        <v>#N/A</v>
+      <c r="L53" t="s">
+        <v>245</v>
       </c>
       <c r="M53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N53" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q53" t="n">
         <v>19.7928</v>
@@ -6254,12 +6256,12 @@
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" t="s">
         <v>242</v>
       </c>
       <c r="D54" t="s">
@@ -6275,10 +6277,10 @@
         <v>-78.73</v>
       </c>
       <c r="H54" t="n">
-        <v>3.027581543</v>
-      </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+        <v>3.02322</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.015</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -6286,20 +6288,20 @@
       <c r="K54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L54" t="e">
-        <v>#N/A</v>
+      <c r="L54" t="s">
+        <v>245</v>
       </c>
       <c r="M54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q54" t="n">
         <v>19.65352</v>
@@ -6331,12 +6333,12 @@
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B55" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" t="s">
         <v>242</v>
       </c>
       <c r="D55" t="s">
@@ -6352,10 +6354,10 @@
         <v>-78.73</v>
       </c>
       <c r="H55" t="n">
-        <v>3.04266333</v>
-      </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+        <v>3.04193</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.015</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -6363,20 +6365,20 @@
       <c r="K55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L55" t="e">
-        <v>#N/A</v>
+      <c r="L55" t="s">
+        <v>245</v>
       </c>
       <c r="M55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q55" t="n">
         <v>19.45939</v>
@@ -6408,12 +6410,12 @@
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" t="s">
         <v>242</v>
       </c>
       <c r="D56" t="s">
@@ -6429,10 +6431,10 @@
         <v>-78.73</v>
       </c>
       <c r="H56" t="n">
-        <v>3.050016113</v>
-      </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+        <v>3.05127</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.015</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -6440,20 +6442,20 @@
       <c r="K56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L56" t="e">
-        <v>#N/A</v>
+      <c r="L56" t="s">
+        <v>245</v>
       </c>
       <c r="M56" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q56" t="n">
         <v>19.58144</v>
@@ -6485,12 +6487,12 @@
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" t="s">
         <v>242</v>
       </c>
       <c r="D57" t="s">
@@ -6506,10 +6508,10 @@
         <v>-78.73</v>
       </c>
       <c r="H57" t="n">
-        <v>3.059026123</v>
-      </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+        <v>3.0608</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.015</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -6517,20 +6519,20 @@
       <c r="K57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L57" t="e">
-        <v>#N/A</v>
+      <c r="L57" t="s">
+        <v>245</v>
       </c>
       <c r="M57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N57" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q57" t="n">
         <v>19.83933</v>
@@ -6562,12 +6564,12 @@
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" t="s">
         <v>242</v>
       </c>
       <c r="D58" t="s">
@@ -6583,10 +6585,10 @@
         <v>-78.73</v>
       </c>
       <c r="H58" t="n">
-        <v>3.062960938</v>
-      </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+        <v>3.06467</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.015</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -6594,20 +6596,20 @@
       <c r="K58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L58" t="e">
-        <v>#N/A</v>
+      <c r="L58" t="s">
+        <v>245</v>
       </c>
       <c r="M58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N58" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O58" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P58" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q58" t="n">
         <v>19.52278</v>
@@ -6639,12 +6641,12 @@
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B59" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" t="s">
         <v>242</v>
       </c>
       <c r="D59" t="s">
@@ -6660,10 +6662,10 @@
         <v>-78.73</v>
       </c>
       <c r="H59" t="n">
-        <v>3.066538086</v>
-      </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+        <v>3.06799</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.015</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -6671,20 +6673,20 @@
       <c r="K59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L59" t="e">
-        <v>#N/A</v>
+      <c r="L59" t="s">
+        <v>245</v>
       </c>
       <c r="M59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q59" t="n">
         <v>19.6676</v>
@@ -6716,12 +6718,12 @@
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B60" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" t="s">
         <v>242</v>
       </c>
       <c r="D60" t="s">
@@ -6737,10 +6739,10 @@
         <v>-78.73</v>
       </c>
       <c r="H60" t="n">
-        <v>3.09118335</v>
-      </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+        <v>3.0912</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.015</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -6748,20 +6750,20 @@
       <c r="K60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L60" t="e">
-        <v>#N/A</v>
+      <c r="L60" t="s">
+        <v>245</v>
       </c>
       <c r="M60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q60" t="n">
         <v>20.03352</v>
@@ -6793,12 +6795,12 @@
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B61" t="s">
         <v>241</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" t="s">
         <v>242</v>
       </c>
       <c r="D61" t="s">
@@ -6814,10 +6816,10 @@
         <v>-78.73</v>
       </c>
       <c r="H61" t="n">
-        <v>3.100177002</v>
-      </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+        <v>3.09949</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.015</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -6825,20 +6827,20 @@
       <c r="K61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L61" t="e">
-        <v>#N/A</v>
+      <c r="L61" t="s">
+        <v>245</v>
       </c>
       <c r="M61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q61" t="n">
         <v>20.10444</v>
@@ -6870,12 +6872,12 @@
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B62" t="s">
         <v>241</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" t="s">
         <v>242</v>
       </c>
       <c r="D62" t="s">
@@ -6891,10 +6893,10 @@
         <v>-78.73</v>
       </c>
       <c r="H62" t="n">
-        <v>3.114238281</v>
-      </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+        <v>3.1122</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.015</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -6902,20 +6904,20 @@
       <c r="K62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L62" t="e">
-        <v>#N/A</v>
+      <c r="L62" t="s">
+        <v>245</v>
       </c>
       <c r="M62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q62" t="n">
         <v>19.60958</v>
@@ -6947,12 +6949,12 @@
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B63" t="s">
         <v>241</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" t="s">
         <v>242</v>
       </c>
       <c r="D63" t="s">
@@ -6968,10 +6970,10 @@
         <v>-78.73</v>
       </c>
       <c r="H63" t="n">
-        <v>3.133154785</v>
-      </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+        <v>3.13459</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.015</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -6979,20 +6981,20 @@
       <c r="K63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L63" t="e">
-        <v>#N/A</v>
+      <c r="L63" t="s">
+        <v>245</v>
       </c>
       <c r="M63" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P63" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q63" t="n">
         <v>19.80492</v>
@@ -7024,12 +7026,12 @@
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B64" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" t="s">
         <v>242</v>
       </c>
       <c r="D64" t="s">
@@ -7045,10 +7047,10 @@
         <v>-78.73</v>
       </c>
       <c r="H64" t="n">
-        <v>3.143166016</v>
-      </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
+        <v>3.14671</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.015</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -7056,20 +7058,20 @@
       <c r="K64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L64" t="e">
-        <v>#N/A</v>
+      <c r="L64" t="s">
+        <v>245</v>
       </c>
       <c r="M64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q64" t="n">
         <v>19.95084</v>
@@ -7101,12 +7103,12 @@
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B65" t="s">
         <v>241</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" t="s">
         <v>242</v>
       </c>
       <c r="D65" t="s">
@@ -7122,10 +7124,10 @@
         <v>-78.73</v>
       </c>
       <c r="H65" t="n">
-        <v>3.151899902</v>
-      </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
+        <v>3.15175</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.015</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -7133,20 +7135,20 @@
       <c r="K65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L65" t="e">
-        <v>#N/A</v>
+      <c r="L65" t="s">
+        <v>245</v>
       </c>
       <c r="M65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q65" t="n">
         <v>19.50743</v>
@@ -7178,12 +7180,12 @@
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" t="s">
         <v>242</v>
       </c>
       <c r="D66" t="s">
@@ -7199,10 +7201,10 @@
         <v>-78.73</v>
       </c>
       <c r="H66" t="n">
-        <v>3.157937012</v>
-      </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
+        <v>3.15435</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.015</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -7210,20 +7212,20 @@
       <c r="K66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L66" t="e">
-        <v>#N/A</v>
+      <c r="L66" t="s">
+        <v>245</v>
       </c>
       <c r="M66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q66" t="n">
         <v>19.93</v>
@@ -7255,12 +7257,12 @@
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" t="s">
         <v>242</v>
       </c>
       <c r="D67" t="s">
@@ -7276,10 +7278,10 @@
         <v>-78.73</v>
       </c>
       <c r="H67" t="n">
-        <v>3.171554932</v>
-      </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
+        <v>3.16038</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.015</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -7287,20 +7289,20 @@
       <c r="K67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L67" t="e">
-        <v>#N/A</v>
+      <c r="L67" t="s">
+        <v>245</v>
       </c>
       <c r="M67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q67" t="n">
         <v>19.40648</v>
@@ -7332,12 +7334,12 @@
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s">
         <v>241</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" t="s">
         <v>242</v>
       </c>
       <c r="D68" t="s">
@@ -7353,10 +7355,10 @@
         <v>-78.73</v>
       </c>
       <c r="H68" t="n">
-        <v>3.179787109</v>
-      </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
+        <v>3.17665</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.015</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -7364,20 +7366,20 @@
       <c r="K68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L68" t="e">
-        <v>#N/A</v>
+      <c r="L68" t="s">
+        <v>245</v>
       </c>
       <c r="M68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q68" t="n">
         <v>19.74612</v>
@@ -7409,12 +7411,12 @@
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" t="s">
         <v>242</v>
       </c>
       <c r="D69" t="s">
@@ -7430,10 +7432,10 @@
         <v>-78.73</v>
       </c>
       <c r="H69" t="n">
-        <v>3.189189941</v>
-      </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
+        <v>3.18088</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.015</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -7441,20 +7443,20 @@
       <c r="K69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L69" t="e">
-        <v>#N/A</v>
+      <c r="L69" t="s">
+        <v>245</v>
       </c>
       <c r="M69" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q69" t="n">
         <v>20.46383</v>
@@ -7486,12 +7488,12 @@
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B70" t="s">
         <v>241</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
@@ -7507,10 +7509,10 @@
         <v>-78.73</v>
       </c>
       <c r="H70" t="n">
-        <v>3.198729248</v>
-      </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
+        <v>3.18478</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.015</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -7518,20 +7520,20 @@
       <c r="K70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L70" t="e">
-        <v>#N/A</v>
+      <c r="L70" t="s">
+        <v>245</v>
       </c>
       <c r="M70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N70" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70" t="n">
         <v>20.0614</v>
@@ -7563,12 +7565,12 @@
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B71" t="s">
         <v>241</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
@@ -7584,10 +7586,10 @@
         <v>-78.73</v>
       </c>
       <c r="H71" t="n">
-        <v>3.209375244</v>
-      </c>
-      <c r="I71" t="e">
-        <v>#N/A</v>
+        <v>3.19203</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.015</v>
       </c>
       <c r="J71" t="e">
         <v>#N/A</v>
@@ -7595,20 +7597,20 @@
       <c r="K71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L71" t="e">
-        <v>#N/A</v>
+      <c r="L71" t="s">
+        <v>245</v>
       </c>
       <c r="M71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" t="n">
         <v>20.12325</v>
@@ -7640,12 +7642,12 @@
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B72" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
@@ -7661,10 +7663,10 @@
         <v>-78.73</v>
       </c>
       <c r="H72" t="n">
-        <v>3.224604492</v>
-      </c>
-      <c r="I72" t="e">
-        <v>#N/A</v>
+        <v>3.20469</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.015</v>
       </c>
       <c r="J72" t="e">
         <v>#N/A</v>
@@ -7672,20 +7674,20 @@
       <c r="K72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L72" t="e">
-        <v>#N/A</v>
+      <c r="L72" t="s">
+        <v>245</v>
       </c>
       <c r="M72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72" t="n">
         <v>19.76645</v>
@@ -7717,12 +7719,12 @@
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s">
         <v>241</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
@@ -7738,10 +7740,10 @@
         <v>-78.73</v>
       </c>
       <c r="H73" t="n">
-        <v>3.239885986</v>
-      </c>
-      <c r="I73" t="e">
-        <v>#N/A</v>
+        <v>3.21795</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.015</v>
       </c>
       <c r="J73" t="e">
         <v>#N/A</v>
@@ -7749,20 +7751,20 @@
       <c r="K73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L73" t="e">
-        <v>#N/A</v>
+      <c r="L73" t="s">
+        <v>245</v>
       </c>
       <c r="M73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73" t="n">
         <v>19.47</v>
@@ -7794,12 +7796,12 @@
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B74" t="s">
         <v>241</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
@@ -7815,10 +7817,10 @@
         <v>-78.73</v>
       </c>
       <c r="H74" t="n">
-        <v>3.242925293</v>
-      </c>
-      <c r="I74" t="e">
-        <v>#N/A</v>
+        <v>3.22067</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.015</v>
       </c>
       <c r="J74" t="e">
         <v>#N/A</v>
@@ -7826,20 +7828,20 @@
       <c r="K74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L74" t="e">
-        <v>#N/A</v>
+      <c r="L74" t="s">
+        <v>245</v>
       </c>
       <c r="M74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q74" t="n">
         <v>19.8293</v>
@@ -7871,12 +7873,12 @@
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B75" t="s">
         <v>241</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
@@ -7892,10 +7894,10 @@
         <v>-78.73</v>
       </c>
       <c r="H75" t="n">
-        <v>3.245811768</v>
-      </c>
-      <c r="I75" t="e">
-        <v>#N/A</v>
+        <v>3.22308</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.015</v>
       </c>
       <c r="J75" t="e">
         <v>#N/A</v>
@@ -7903,20 +7905,20 @@
       <c r="K75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L75" t="e">
-        <v>#N/A</v>
+      <c r="L75" t="s">
+        <v>245</v>
       </c>
       <c r="M75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q75" t="n">
         <v>20.1553</v>
@@ -7948,12 +7950,12 @@
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B76" t="s">
         <v>241</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
@@ -7969,10 +7971,10 @@
         <v>-78.73</v>
       </c>
       <c r="H76" t="n">
-        <v>3.259577881</v>
-      </c>
-      <c r="I76" t="e">
-        <v>#N/A</v>
+        <v>3.23513</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.015</v>
       </c>
       <c r="J76" t="e">
         <v>#N/A</v>
@@ -7980,20 +7982,20 @@
       <c r="K76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L76" t="e">
-        <v>#N/A</v>
+      <c r="L76" t="s">
+        <v>245</v>
       </c>
       <c r="M76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76" t="n">
         <v>19.89508</v>
@@ -8025,12 +8027,12 @@
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B77" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
@@ -8046,10 +8048,10 @@
         <v>-78.73</v>
       </c>
       <c r="H77" t="n">
-        <v>3.270168457</v>
-      </c>
-      <c r="I77" t="e">
-        <v>#N/A</v>
+        <v>3.25214</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.015</v>
       </c>
       <c r="J77" t="e">
         <v>#N/A</v>
@@ -8057,20 +8059,20 @@
       <c r="K77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L77" t="e">
-        <v>#N/A</v>
+      <c r="L77" t="s">
+        <v>245</v>
       </c>
       <c r="M77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77" t="n">
         <v>19.91711</v>
@@ -8102,12 +8104,12 @@
     </row>
     <row r="78" ht="19" customHeight="1">
       <c r="A78" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B78" t="s">
         <v>241</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
@@ -8123,10 +8125,10 @@
         <v>-78.73</v>
       </c>
       <c r="H78" t="n">
-        <v>3.280600586</v>
-      </c>
-      <c r="I78" t="e">
-        <v>#N/A</v>
+        <v>3.27206</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.015</v>
       </c>
       <c r="J78" t="e">
         <v>#N/A</v>
@@ -8134,20 +8136,20 @@
       <c r="K78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L78" t="e">
-        <v>#N/A</v>
+      <c r="L78" t="s">
+        <v>245</v>
       </c>
       <c r="M78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N78" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q78" t="n">
         <v>20.14843</v>
@@ -8179,12 +8181,12 @@
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
@@ -8202,8 +8204,8 @@
       <c r="H79" t="n">
         <v>2.347234375</v>
       </c>
-      <c r="I79" t="e">
-        <v>#N/A</v>
+      <c r="I79" t="n">
+        <v>0.006</v>
       </c>
       <c r="J79" t="e">
         <v>#N/A</v>
@@ -8211,20 +8213,20 @@
       <c r="K79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L79" t="e">
-        <v>#N/A</v>
+      <c r="L79" t="s">
+        <v>325</v>
       </c>
       <c r="M79" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N79" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79" t="n">
         <v>19.79990497</v>
@@ -8256,12 +8258,12 @@
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B80" t="s">
         <v>241</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" t="s">
         <v>242</v>
       </c>
       <c r="D80" t="s">
@@ -8279,8 +8281,8 @@
       <c r="H80" t="n">
         <v>2.417172607</v>
       </c>
-      <c r="I80" t="e">
-        <v>#N/A</v>
+      <c r="I80" t="n">
+        <v>0.006</v>
       </c>
       <c r="J80" t="e">
         <v>#N/A</v>
@@ -8288,20 +8290,20 @@
       <c r="K80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L80" t="e">
-        <v>#N/A</v>
+      <c r="L80" t="s">
+        <v>325</v>
       </c>
       <c r="M80" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N80" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q80" t="n">
         <v>19.39170408</v>
@@ -8333,12 +8335,12 @@
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s">
         <v>241</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" t="s">
         <v>242</v>
       </c>
       <c r="D81" t="s">
@@ -8356,8 +8358,8 @@
       <c r="H81" t="n">
         <v>2.498358643</v>
       </c>
-      <c r="I81" t="e">
-        <v>#N/A</v>
+      <c r="I81" t="n">
+        <v>0.006</v>
       </c>
       <c r="J81" t="e">
         <v>#N/A</v>
@@ -8365,20 +8367,20 @@
       <c r="K81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L81" t="e">
-        <v>#N/A</v>
+      <c r="L81" t="s">
+        <v>325</v>
       </c>
       <c r="M81" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N81" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81" t="n">
         <v>19.4612479</v>
@@ -8410,12 +8412,12 @@
     </row>
     <row r="82" ht="19" customHeight="1">
       <c r="A82" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B82" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" t="s">
         <v>242</v>
       </c>
       <c r="D82" t="s">
@@ -8433,8 +8435,8 @@
       <c r="H82" t="n">
         <v>2.626144531</v>
       </c>
-      <c r="I82" t="e">
-        <v>#N/A</v>
+      <c r="I82" t="n">
+        <v>0.006</v>
       </c>
       <c r="J82" t="e">
         <v>#N/A</v>
@@ -8442,20 +8444,20 @@
       <c r="K82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L82" t="e">
-        <v>#N/A</v>
+      <c r="L82" t="s">
+        <v>325</v>
       </c>
       <c r="M82" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N82" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q82" t="n">
         <v>19.54310365</v>
@@ -8487,12 +8489,12 @@
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B83" t="s">
         <v>241</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" t="s">
         <v>242</v>
       </c>
       <c r="D83" t="s">
@@ -8510,8 +8512,8 @@
       <c r="H83" t="n">
         <v>2.750568604</v>
       </c>
-      <c r="I83" t="e">
-        <v>#N/A</v>
+      <c r="I83" t="n">
+        <v>0.006</v>
       </c>
       <c r="J83" t="e">
         <v>#N/A</v>
@@ -8519,20 +8521,20 @@
       <c r="K83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L83" t="e">
-        <v>#N/A</v>
+      <c r="L83" t="s">
+        <v>325</v>
       </c>
       <c r="M83" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N83" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83" t="n">
         <v>19.70604062</v>
@@ -8564,12 +8566,12 @@
     </row>
     <row r="84" ht="19" customHeight="1">
       <c r="A84" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B84" t="s">
         <v>241</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" t="s">
         <v>242</v>
       </c>
       <c r="D84" t="s">
@@ -8587,8 +8589,8 @@
       <c r="H84" t="n">
         <v>2.828275879</v>
       </c>
-      <c r="I84" t="e">
-        <v>#N/A</v>
+      <c r="I84" t="n">
+        <v>0.006</v>
       </c>
       <c r="J84" t="e">
         <v>#N/A</v>
@@ -8596,20 +8598,20 @@
       <c r="K84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L84" t="e">
-        <v>#N/A</v>
+      <c r="L84" t="s">
+        <v>325</v>
       </c>
       <c r="M84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N84" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O84" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q84" t="n">
         <v>19.76559175</v>
@@ -8641,12 +8643,12 @@
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="A85" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B85" t="s">
         <v>241</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" t="s">
         <v>242</v>
       </c>
       <c r="D85" t="s">
@@ -8664,8 +8666,8 @@
       <c r="H85" t="n">
         <v>3.160107422</v>
       </c>
-      <c r="I85" t="e">
-        <v>#N/A</v>
+      <c r="I85" t="n">
+        <v>0.015</v>
       </c>
       <c r="J85" t="e">
         <v>#N/A</v>
@@ -8673,20 +8675,20 @@
       <c r="K85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L85" t="e">
-        <v>#N/A</v>
+      <c r="L85" t="s">
+        <v>325</v>
       </c>
       <c r="M85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N85" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P85" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q85" t="n">
         <v>18.99292811</v>
@@ -8718,12 +8720,12 @@
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B86" t="s">
         <v>241</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" t="s">
         <v>242</v>
       </c>
       <c r="D86" t="s">
@@ -8741,8 +8743,8 @@
       <c r="H86" t="n">
         <v>3.2449021</v>
       </c>
-      <c r="I86" t="e">
-        <v>#N/A</v>
+      <c r="I86" t="n">
+        <v>0.015</v>
       </c>
       <c r="J86" t="e">
         <v>#N/A</v>
@@ -8750,20 +8752,20 @@
       <c r="K86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L86" t="e">
-        <v>#N/A</v>
+      <c r="L86" t="s">
+        <v>325</v>
       </c>
       <c r="M86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q86" t="n">
         <v>19.29490774</v>
@@ -8859,90 +8861,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-    <hyperlink ref="C85" r:id="rId81h"/>
-    <hyperlink ref="C86" r:id="rId82h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
